--- a/research/traditional_assets/database/data/thailand/thailand_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_reinsurance.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0387</v>
+        <v>0.032975</v>
       </c>
       <c r="E2">
-        <v>-0.188</v>
+        <v>-0.178</v>
       </c>
       <c r="G2">
-        <v>0.06532964499769479</v>
+        <v>-0.04444444444444445</v>
       </c>
       <c r="H2">
-        <v>0.06532964499769479</v>
+        <v>-0.04444444444444445</v>
       </c>
       <c r="I2">
-        <v>-0.006362378976486859</v>
+        <v>-0.03202020202020202</v>
       </c>
       <c r="J2">
-        <v>-0.005876793604285642</v>
+        <v>-0.02939797148439123</v>
       </c>
       <c r="K2">
-        <v>-0.54</v>
+        <v>-5.7</v>
       </c>
       <c r="L2">
-        <v>-0.002489626556016598</v>
+        <v>-0.02878787878787879</v>
       </c>
       <c r="M2">
-        <v>7.51</v>
+        <v>3.18</v>
       </c>
       <c r="N2">
-        <v>0.03697685869030035</v>
+        <v>0.01634121274409044</v>
       </c>
       <c r="O2">
-        <v>-13.90740740740741</v>
+        <v>-0.5578947368421052</v>
       </c>
       <c r="P2">
-        <v>7.51</v>
+        <v>3.18</v>
       </c>
       <c r="Q2">
-        <v>0.03697685869030035</v>
+        <v>0.01634121274409044</v>
       </c>
       <c r="R2">
-        <v>-13.90740740740741</v>
+        <v>-0.5578947368421052</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>16.39</v>
+        <v>13.7</v>
       </c>
       <c r="V2">
-        <v>0.08069916297390449</v>
+        <v>0.07040082219938334</v>
       </c>
       <c r="W2">
-        <v>0.02758120251753528</v>
+        <v>-0.001343401776118566</v>
       </c>
       <c r="X2">
-        <v>0.09556366753955947</v>
+        <v>0.1337060169008191</v>
       </c>
       <c r="Y2">
-        <v>-0.06798246502202419</v>
+        <v>-0.1350494186769376</v>
       </c>
       <c r="Z2">
-        <v>1.528810572687225</v>
+        <v>1.57094232737486</v>
       </c>
       <c r="AA2">
-        <v>0.01908386471819655</v>
+        <v>-0.01355012600729465</v>
       </c>
       <c r="AB2">
-        <v>0.09550459063039821</v>
+        <v>0.1336652873186996</v>
       </c>
       <c r="AC2">
-        <v>-0.07642072591220166</v>
+        <v>-0.1472154133259942</v>
       </c>
       <c r="AD2">
-        <v>0.229</v>
+        <v>0.13</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.229</v>
+        <v>0.13</v>
       </c>
       <c r="AG2">
-        <v>-16.161</v>
+        <v>-13.57</v>
       </c>
       <c r="AH2">
-        <v>0.001126253510320712</v>
+        <v>0.0006675910234683921</v>
       </c>
       <c r="AI2">
-        <v>0.001607818632441427</v>
+        <v>0.001083965646627199</v>
       </c>
       <c r="AJ2">
-        <v>-0.08645066037584453</v>
+        <v>-0.07495995138927247</v>
       </c>
       <c r="AK2">
-        <v>-0.1282222169328541</v>
+        <v>-0.1277416925538925</v>
       </c>
       <c r="AL2">
-        <v>0.014</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="AM2">
-        <v>0.014</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="AN2">
-        <v>-0.2160377358490567</v>
+        <v>-0.02574257425742574</v>
       </c>
       <c r="AO2">
-        <v>-98.57142857142856</v>
+        <v>-704.4444444444442</v>
       </c>
       <c r="AP2">
-        <v>15.24622641509435</v>
+        <v>2.687128712871287</v>
       </c>
       <c r="AQ2">
-        <v>-98.57142857142856</v>
+        <v>-704.4444444444442</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0658</v>
+        <v>0.0604</v>
       </c>
       <c r="E3">
-        <v>-0.188</v>
+        <v>-0.178</v>
       </c>
       <c r="G3">
-        <v>0.06223067173637516</v>
+        <v>0.04627249357326479</v>
       </c>
       <c r="H3">
-        <v>0.06223067173637516</v>
+        <v>0.04627249357326479</v>
       </c>
       <c r="I3">
-        <v>0.05994930291508238</v>
+        <v>0.06246786632390746</v>
       </c>
       <c r="J3">
-        <v>0.05079847908745247</v>
+        <v>0.05223650385604114</v>
       </c>
       <c r="K3">
-        <v>4.01</v>
+        <v>4.06</v>
       </c>
       <c r="L3">
-        <v>0.05082382762991127</v>
+        <v>0.05218508997429305</v>
       </c>
       <c r="M3">
-        <v>2.5</v>
+        <v>3.18</v>
       </c>
       <c r="N3">
-        <v>0.0423728813559322</v>
+        <v>0.04303112313937753</v>
       </c>
       <c r="O3">
-        <v>0.6234413965087282</v>
+        <v>0.7832512315270937</v>
       </c>
       <c r="P3">
-        <v>2.5</v>
+        <v>3.18</v>
       </c>
       <c r="Q3">
-        <v>0.0423728813559322</v>
+        <v>0.04303112313937753</v>
       </c>
       <c r="R3">
-        <v>0.6234413965087282</v>
+        <v>0.7832512315270937</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.99</v>
+        <v>0.7</v>
       </c>
       <c r="V3">
-        <v>0.05067796610169492</v>
+        <v>0.009472259810554802</v>
       </c>
       <c r="W3">
-        <v>0.09593301435406698</v>
+        <v>0.09530516431924882</v>
       </c>
       <c r="X3">
-        <v>0.09553406975993969</v>
+        <v>0.1336692867716013</v>
       </c>
       <c r="Y3">
-        <v>0.0003989445941272873</v>
+        <v>-0.03836412245235246</v>
       </c>
       <c r="Z3">
-        <v>1.939861824797778</v>
+        <v>1.962763005197033</v>
       </c>
       <c r="AA3">
-        <v>0.0985420303395373</v>
+        <v>0.1025278772894697</v>
       </c>
       <c r="AB3">
-        <v>0.09550276838445136</v>
+        <v>0.1336644844545564</v>
       </c>
       <c r="AC3">
-        <v>0.003039261955085942</v>
+        <v>-0.03113660716508675</v>
       </c>
       <c r="AD3">
-        <v>0.028</v>
+        <v>0.005</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.028</v>
+        <v>0.005</v>
       </c>
       <c r="AG3">
-        <v>-2.962</v>
+        <v>-0.695</v>
       </c>
       <c r="AH3">
-        <v>0.0004743511553838856</v>
+        <v>6.76544212164265e-05</v>
       </c>
       <c r="AI3">
-        <v>0.0006568452660223327</v>
+        <v>0.0001326084073730274</v>
       </c>
       <c r="AJ3">
-        <v>-0.05285698989971092</v>
+        <v>-0.009493887029574479</v>
       </c>
       <c r="AK3">
-        <v>-0.07472627276855544</v>
+        <v>-0.01878124577759762</v>
       </c>
       <c r="AL3">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AM3">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AN3">
-        <v>0.005714285714285714</v>
+        <v>0.0009900990099009901</v>
       </c>
       <c r="AO3">
-        <v>2365</v>
+        <v>4860</v>
       </c>
       <c r="AP3">
-        <v>-0.6044897959183674</v>
+        <v>-0.1376237623762376</v>
       </c>
       <c r="AQ3">
-        <v>2365</v>
+        <v>4860</v>
       </c>
     </row>
     <row r="4">
@@ -856,118 +856,115 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0116</v>
+        <v>0.00555</v>
       </c>
       <c r="G4">
-        <v>0.06710144927536232</v>
+        <v>-0.1031613976705491</v>
       </c>
       <c r="H4">
-        <v>0.06710144927536232</v>
+        <v>-0.1031613976705491</v>
       </c>
       <c r="I4">
-        <v>-0.04427536231884058</v>
+        <v>-0.09317803660565722</v>
       </c>
       <c r="J4">
-        <v>-0.04427536231884058</v>
+        <v>-0.09317803660565722</v>
       </c>
       <c r="K4">
-        <v>-4.55</v>
+        <v>-9.76</v>
       </c>
       <c r="L4">
-        <v>-0.03297101449275362</v>
+        <v>-0.08119800332778702</v>
       </c>
       <c r="M4">
-        <v>5.01</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.0347675225537821</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>-1.101098901098901</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>5.01</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.0347675225537821</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>-1.101098901098901</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>13.4</v>
+        <v>13</v>
       </c>
       <c r="V4">
-        <v>0.0929909784871617</v>
+        <v>0.1077050538525269</v>
       </c>
       <c r="W4">
-        <v>-0.04077060931899642</v>
+        <v>-0.09799196787148595</v>
       </c>
       <c r="X4">
-        <v>0.09559326531917924</v>
+        <v>0.1337427470300369</v>
       </c>
       <c r="Y4">
-        <v>-0.1363638746381756</v>
+        <v>-0.2317347149015229</v>
       </c>
       <c r="Z4">
-        <v>1.363609414833699</v>
+        <v>1.391187601995348</v>
       </c>
       <c r="AA4">
-        <v>-0.06037430090314421</v>
+        <v>-0.129628129304059</v>
       </c>
       <c r="AB4">
-        <v>0.09550641287634504</v>
+        <v>0.1336660901828427</v>
       </c>
       <c r="AC4">
-        <v>-0.1558807137794893</v>
+        <v>-0.2632942194869017</v>
       </c>
       <c r="AD4">
-        <v>0.201</v>
+        <v>0.125</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.201</v>
+        <v>0.125</v>
       </c>
       <c r="AG4">
-        <v>-13.199</v>
+        <v>-12.875</v>
       </c>
       <c r="AH4">
-        <v>0.001392921739974082</v>
+        <v>0.001034554107179805</v>
       </c>
       <c r="AI4">
-        <v>0.002014007875672589</v>
+        <v>0.001520218911523259</v>
       </c>
       <c r="AJ4">
-        <v>-0.1008319264176744</v>
+        <v>-0.1194064456294922</v>
       </c>
       <c r="AK4">
-        <v>-0.1527644355968102</v>
+        <v>-0.1859877211989888</v>
       </c>
       <c r="AL4">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
       <c r="AM4">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
       <c r="AN4">
-        <v>-0.0337248322147651</v>
+        <v>-0.01237623762376238</v>
       </c>
       <c r="AO4">
-        <v>-509.1666666666667</v>
+        <v>-1400</v>
       </c>
       <c r="AP4">
-        <v>2.214597315436241</v>
+        <v>1.274752475247525</v>
       </c>
       <c r="AQ4">
-        <v>-509.1666666666667</v>
+        <v>-1400</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/thailand/thailand_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_reinsurance.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.032975</v>
+        <v>0.044</v>
       </c>
       <c r="E2">
-        <v>-0.178</v>
+        <v>-0.277</v>
       </c>
       <c r="G2">
-        <v>-0.04444444444444445</v>
+        <v>-0.00156537753222836</v>
       </c>
       <c r="H2">
-        <v>-0.04444444444444445</v>
+        <v>-0.00156537753222836</v>
       </c>
       <c r="I2">
-        <v>-0.03202020202020202</v>
+        <v>0.0322744014732965</v>
       </c>
       <c r="J2">
-        <v>-0.02939797148439123</v>
+        <v>0.02921590674884151</v>
       </c>
       <c r="K2">
-        <v>-5.7</v>
+        <v>5.75</v>
       </c>
       <c r="L2">
-        <v>-0.02878787878787879</v>
+        <v>0.02647329650092081</v>
       </c>
       <c r="M2">
-        <v>3.18</v>
+        <v>1.15</v>
       </c>
       <c r="N2">
-        <v>0.01634121274409044</v>
+        <v>0.0079750346740638</v>
       </c>
       <c r="O2">
-        <v>-0.5578947368421052</v>
+        <v>0.2</v>
       </c>
       <c r="P2">
-        <v>3.18</v>
+        <v>1.15</v>
       </c>
       <c r="Q2">
-        <v>0.01634121274409044</v>
+        <v>0.0079750346740638</v>
       </c>
       <c r="R2">
-        <v>-0.5578947368421052</v>
+        <v>0.2</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>13.7</v>
+        <v>8.793999999999999</v>
       </c>
       <c r="V2">
-        <v>0.07040082219938334</v>
+        <v>0.06098474341192787</v>
       </c>
       <c r="W2">
-        <v>-0.001343401776118566</v>
+        <v>0.04685283845475369</v>
       </c>
       <c r="X2">
-        <v>0.1337060169008191</v>
+        <v>0.1132198390766113</v>
       </c>
       <c r="Y2">
-        <v>-0.1350494186769376</v>
+        <v>-0.06636700062185766</v>
       </c>
       <c r="Z2">
-        <v>1.57094232737486</v>
+        <v>2.044620163795538</v>
       </c>
       <c r="AA2">
-        <v>-0.01355012600729465</v>
+        <v>0.0521395048982625</v>
       </c>
       <c r="AB2">
-        <v>0.1336652873186996</v>
+        <v>0.1130643383724848</v>
       </c>
       <c r="AC2">
-        <v>-0.1472154133259942</v>
+        <v>-0.06092483347422231</v>
       </c>
       <c r="AD2">
-        <v>0.13</v>
+        <v>0.404</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.13</v>
+        <v>0.404</v>
       </c>
       <c r="AG2">
-        <v>-13.57</v>
+        <v>-8.389999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.0006675910234683921</v>
+        <v>0.00279383696163315</v>
       </c>
       <c r="AI2">
-        <v>0.001083965646627199</v>
+        <v>0.002883572203505967</v>
       </c>
       <c r="AJ2">
-        <v>-0.07495995138927247</v>
+        <v>-0.0617774832486562</v>
       </c>
       <c r="AK2">
-        <v>-0.1277416925538925</v>
+        <v>-0.0638946005635519</v>
       </c>
       <c r="AL2">
-        <v>0.009000000000000001</v>
+        <v>0.022</v>
       </c>
       <c r="AM2">
-        <v>0.009000000000000001</v>
+        <v>0.022</v>
       </c>
       <c r="AN2">
-        <v>-0.02574257425742574</v>
+        <v>0.05139949109414759</v>
       </c>
       <c r="AO2">
-        <v>-704.4444444444442</v>
+        <v>318.6363636363636</v>
       </c>
       <c r="AP2">
-        <v>2.687128712871287</v>
+        <v>-1.067430025445293</v>
       </c>
       <c r="AQ2">
-        <v>-704.4444444444442</v>
+        <v>318.6363636363636</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Thaire Life Assurance Public Company Limited (SET:THREL)</t>
+          <t>Thai Reinsurance Public Company Limited (SET:THRE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,121 +722,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0604</v>
-      </c>
-      <c r="E3">
-        <v>-0.178</v>
+        <v>0.03240000000000001</v>
       </c>
       <c r="G3">
-        <v>0.04627249357326479</v>
+        <v>-0.04486486486486486</v>
       </c>
       <c r="H3">
-        <v>0.04627249357326479</v>
+        <v>-0.04486486486486486</v>
       </c>
       <c r="I3">
-        <v>0.06246786632390746</v>
+        <v>0.04293436293436293</v>
       </c>
       <c r="J3">
-        <v>0.05223650385604114</v>
+        <v>0.0347969836778501</v>
       </c>
       <c r="K3">
-        <v>4.06</v>
+        <v>4.1</v>
       </c>
       <c r="L3">
-        <v>0.05218508997429305</v>
+        <v>0.03166023166023166</v>
       </c>
       <c r="M3">
-        <v>3.18</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.04303112313937753</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.7832512315270937</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>3.18</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.04303112313937753</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.7832512315270937</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>0.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="V3">
-        <v>0.009472259810554802</v>
+        <v>0.0841889117043121</v>
       </c>
       <c r="W3">
-        <v>0.09530516431924882</v>
+        <v>0.04993909866017052</v>
       </c>
       <c r="X3">
-        <v>0.1336692867716013</v>
+        <v>0.1132659996392586</v>
       </c>
       <c r="Y3">
-        <v>-0.03836412245235246</v>
+        <v>-0.06332690097908805</v>
       </c>
       <c r="Z3">
-        <v>1.962763005197033</v>
+        <v>1.870711448176237</v>
       </c>
       <c r="AA3">
-        <v>0.1025278772894697</v>
+        <v>0.06509511572815585</v>
       </c>
       <c r="AB3">
-        <v>0.1336644844545564</v>
+        <v>0.113057421128546</v>
       </c>
       <c r="AC3">
-        <v>-0.03113660716508675</v>
+        <v>-0.04796230540039018</v>
       </c>
       <c r="AD3">
-        <v>0.005</v>
+        <v>0.322</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.005</v>
+        <v>0.322</v>
       </c>
       <c r="AG3">
-        <v>-0.695</v>
+        <v>-7.877999999999999</v>
       </c>
       <c r="AH3">
-        <v>6.76544212164265e-05</v>
+        <v>0.003295061500992611</v>
       </c>
       <c r="AI3">
-        <v>0.0001326084073730274</v>
+        <v>0.003131625527610823</v>
       </c>
       <c r="AJ3">
-        <v>-0.009493887029574479</v>
+        <v>-0.08800071490806728</v>
       </c>
       <c r="AK3">
-        <v>-0.01878124577759762</v>
+        <v>-0.08325759337152036</v>
       </c>
       <c r="AL3">
-        <v>0.001</v>
+        <v>0.02</v>
       </c>
       <c r="AM3">
-        <v>0.001</v>
+        <v>0.02</v>
       </c>
       <c r="AN3">
-        <v>0.0009900990099009901</v>
+        <v>0.05143769968051119</v>
       </c>
       <c r="AO3">
-        <v>4860</v>
+        <v>278</v>
       </c>
       <c r="AP3">
-        <v>-0.1376237623762376</v>
+        <v>-1.258466453674121</v>
       </c>
       <c r="AQ3">
-        <v>4860</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Thai Reinsurance Public Company Limited (SET:THRE)</t>
+          <t>Thaire Life Assurance Public Company Limited (SET:THREL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,115 +850,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.00555</v>
+        <v>0.0556</v>
+      </c>
+      <c r="E4">
+        <v>-0.277</v>
       </c>
       <c r="G4">
-        <v>-0.1031613976705491</v>
+        <v>0.06237172177879133</v>
       </c>
       <c r="H4">
-        <v>-0.1031613976705491</v>
+        <v>0.06237172177879133</v>
       </c>
       <c r="I4">
-        <v>-0.09317803660565722</v>
+        <v>0.01653363740022805</v>
       </c>
       <c r="J4">
-        <v>-0.09317803660565722</v>
+        <v>0.01653363740022805</v>
       </c>
       <c r="K4">
-        <v>-9.76</v>
+        <v>1.65</v>
       </c>
       <c r="L4">
-        <v>-0.08119800332778702</v>
+        <v>0.01881413911060433</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>1.15</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.02457264957264957</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>0.6969696969696969</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>1.15</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.02457264957264957</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>0.6969696969696969</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>13</v>
+        <v>0.594</v>
       </c>
       <c r="V4">
-        <v>0.1077050538525269</v>
+        <v>0.01269230769230769</v>
       </c>
       <c r="W4">
-        <v>-0.09799196787148595</v>
+        <v>0.04376657824933686</v>
       </c>
       <c r="X4">
-        <v>0.1337427470300369</v>
+        <v>0.1131736785139641</v>
       </c>
       <c r="Y4">
-        <v>-0.2317347149015229</v>
+        <v>-0.06940710026462726</v>
       </c>
       <c r="Z4">
-        <v>1.391187601995348</v>
+        <v>2.369950006755844</v>
       </c>
       <c r="AA4">
-        <v>-0.129628129304059</v>
+        <v>0.03918389406836913</v>
       </c>
       <c r="AB4">
-        <v>0.1336660901828427</v>
+        <v>0.1130712556164236</v>
       </c>
       <c r="AC4">
-        <v>-0.2632942194869017</v>
+        <v>-0.07388736154805445</v>
       </c>
       <c r="AD4">
-        <v>0.125</v>
+        <v>0.082</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.125</v>
+        <v>0.082</v>
       </c>
       <c r="AG4">
-        <v>-12.875</v>
+        <v>-0.512</v>
       </c>
       <c r="AH4">
-        <v>0.001034554107179805</v>
+        <v>0.001749072138560642</v>
       </c>
       <c r="AI4">
-        <v>0.001520218911523259</v>
+        <v>0.002199452819054772</v>
       </c>
       <c r="AJ4">
-        <v>-0.1194064456294922</v>
+        <v>-0.01106118216384376</v>
       </c>
       <c r="AK4">
-        <v>-0.1859877211989888</v>
+        <v>-0.01395551679023114</v>
       </c>
       <c r="AL4">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="AM4">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="AN4">
-        <v>-0.01237623762376238</v>
+        <v>0.05125</v>
       </c>
       <c r="AO4">
-        <v>-1400</v>
+        <v>725</v>
       </c>
       <c r="AP4">
-        <v>1.274752475247525</v>
+        <v>-0.32</v>
       </c>
       <c r="AQ4">
-        <v>-1400</v>
+        <v>725</v>
       </c>
     </row>
   </sheetData>
